--- a/data_guide.xlsx
+++ b/data_guide.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noepa\Desktop\Lab3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denny\workspace\BFMRod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CBDBAF-AF95-4972-A9F6-F0F4B61B8522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085D6AB0-919B-4C4A-8F4A-F958CED719A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{21C689C8-0F5B-4BCC-9819-8EF88FA58E1B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="34890" windowHeight="20175" xr2:uid="{21C689C8-0F5B-4BCC-9819-8EF88FA58E1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="198">
   <si>
     <t>ULTIMATE GUIDE TO DATA TAKEN BETWEEN MARCH AND JUNE 2025 - GOLD NANORODS</t>
   </si>
@@ -414,6 +414,222 @@
   </si>
   <si>
     <t>useless</t>
+  </si>
+  <si>
+    <t>Traj Check</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK </t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>Best Channel</t>
+  </si>
+  <si>
+    <t>C0</t>
+  </si>
+  <si>
+    <t>Itot</t>
+  </si>
+  <si>
+    <t>OK / Good</t>
+  </si>
+  <si>
+    <t>All Similar, Need to check for 2x speed</t>
+  </si>
+  <si>
+    <t>C135</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>not enough data</t>
+  </si>
+  <si>
+    <t>C90? But all seems to be 2x speed</t>
+  </si>
+  <si>
+    <t>C0 but need to check (in segments) 2x speed</t>
+  </si>
+  <si>
+    <t>C45 check for 2x speed for fluctuation</t>
+  </si>
+  <si>
+    <t>Itot check for 2x speed for fluctuation</t>
+  </si>
+  <si>
+    <t>Itot, maybe 2x</t>
+  </si>
+  <si>
+    <t>C0?</t>
+  </si>
+  <si>
+    <t>All looks to be 2x speed</t>
+  </si>
+  <si>
+    <t>C45 need to check if it's 2x speed</t>
+  </si>
+  <si>
+    <t>All C channels</t>
+  </si>
+  <si>
+    <t>C135 Looks interesting comparing to other channels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C90 </t>
+  </si>
+  <si>
+    <t>X+iY</t>
+  </si>
+  <si>
+    <t>C45 / C135 / Itot</t>
+  </si>
+  <si>
+    <t>C45 / C90 / C135</t>
+  </si>
+  <si>
+    <t>C0 / C90?</t>
+  </si>
+  <si>
+    <t>C0 / C45</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>C135?</t>
+  </si>
+  <si>
+    <t>C0? FFT looks bad</t>
+  </si>
+  <si>
+    <t>Looks funny because missing one channel</t>
+  </si>
+  <si>
+    <t>C90</t>
+  </si>
+  <si>
+    <t>Itot? Need to check and compare all</t>
+  </si>
+  <si>
+    <t>C45 / C135</t>
+  </si>
+  <si>
+    <t>C90? But needs some filtering</t>
+  </si>
+  <si>
+    <t>C90 / C135</t>
+  </si>
+  <si>
+    <t>All look the same; need to check for 2x</t>
+  </si>
+  <si>
+    <t>All look the same; need to check for 2x; for this and many other traces x+iy showed switching? Could be interesting to look into as well.</t>
+  </si>
+  <si>
+    <t>C135? Check for 2x</t>
+  </si>
+  <si>
+    <t>?? Not sure, maybe combining Itot and X+iY? Need extra work.</t>
+  </si>
+  <si>
+    <t>If the issue is reduced speed we might need to try FFT at a larger window for this day's data</t>
+  </si>
+  <si>
+    <t>Good (pretzel)</t>
+  </si>
+  <si>
+    <t>C0 / Itot</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+  <si>
+    <t>All seem to be 2x speed</t>
+  </si>
+  <si>
+    <t>Good (helicopter)</t>
+  </si>
+  <si>
+    <t>Probably all 2x speed</t>
+  </si>
+  <si>
+    <t>Itot?</t>
+  </si>
+  <si>
+    <t>Good (pretzel) but very noisy</t>
+  </si>
+  <si>
+    <t>C90 but could be 2x</t>
+  </si>
+  <si>
+    <t>Itot but likely 2x</t>
+  </si>
+  <si>
+    <t>C135 but could be 2x</t>
+  </si>
+  <si>
+    <t>Good (helicopter?) but very noisy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad </t>
+  </si>
+  <si>
+    <t>Itot But could have 2x speed</t>
+  </si>
+  <si>
+    <t>OK?</t>
+  </si>
+  <si>
+    <t>PCA</t>
+  </si>
+  <si>
+    <t>Up to 254s</t>
+  </si>
+  <si>
+    <t>Bad, photodamage?</t>
+  </si>
+  <si>
+    <t>Up to 27s</t>
+  </si>
+  <si>
+    <t>Done (really good)</t>
+  </si>
+  <si>
+    <t>Bad, just noisy</t>
+  </si>
+  <si>
+    <t>Good (helicopter) ?</t>
+  </si>
+  <si>
+    <t>Good (pretzel) PCA no good</t>
+  </si>
+  <si>
+    <t>Good (pretzel) PCA good up to 86s only</t>
+  </si>
+  <si>
+    <t>Good (pretzel)? Not sure what happens but this trace crashed PCA</t>
+  </si>
+  <si>
+    <t>Good (pretzel) pca too messy</t>
+  </si>
+  <si>
+    <t>Good (helicopter) ? pca too messy</t>
+  </si>
+  <si>
+    <t>Good (pretzel) PCA very noisy</t>
+  </si>
+  <si>
+    <t>Good (helicopter) ? PCA very noisy</t>
+  </si>
+  <si>
+    <t>Good (pretzel) PCA noisy</t>
   </si>
 </sst>
 </file>
@@ -833,29 +1049,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{513C6D4C-8706-426F-802E-E2B9E035F594}">
-  <dimension ref="A1:L192"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O192"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" customWidth="1"/>
-    <col min="4" max="4" width="17.90625" customWidth="1"/>
+    <col min="3" max="3" width="35.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" customWidth="1"/>
-    <col min="8" max="8" width="14.08984375" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="4.1796875" customWidth="1"/>
-    <col min="11" max="11" width="4.90625" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" customWidth="1"/>
+    <col min="10" max="10" width="4.140625" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="121.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -892,8 +1111,17 @@
       <c r="L3" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>20250311</v>
       </c>
@@ -924,8 +1152,17 @@
         <v>0</v>
       </c>
       <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M4" t="s">
+        <v>168</v>
+      </c>
+      <c r="N4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>20250311</v>
       </c>
@@ -956,8 +1193,14 @@
         <v>0</v>
       </c>
       <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>20250311</v>
       </c>
@@ -990,8 +1233,14 @@
         <v>0</v>
       </c>
       <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>20250311</v>
       </c>
@@ -1024,8 +1273,14 @@
         <v>0</v>
       </c>
       <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>20250313</v>
       </c>
@@ -1058,8 +1313,14 @@
         <v>0</v>
       </c>
       <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M8" t="s">
+        <v>154</v>
+      </c>
+      <c r="N8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>20250313</v>
       </c>
@@ -1092,8 +1353,14 @@
         <v>0</v>
       </c>
       <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M9" t="s">
+        <v>154</v>
+      </c>
+      <c r="N9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>20250313</v>
       </c>
@@ -1126,8 +1393,17 @@
         <v>0</v>
       </c>
       <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M10" t="s">
+        <v>179</v>
+      </c>
+      <c r="N10" t="s">
+        <v>178</v>
+      </c>
+      <c r="O10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>20250313</v>
       </c>
@@ -1158,8 +1434,14 @@
         <v>0</v>
       </c>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M11" t="s">
+        <v>180</v>
+      </c>
+      <c r="N11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>20250313</v>
       </c>
@@ -1192,8 +1474,14 @@
         <v>0</v>
       </c>
       <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>170</v>
+      </c>
+      <c r="N12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>20250313</v>
       </c>
@@ -1226,8 +1514,14 @@
         <v>0</v>
       </c>
       <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M13" t="s">
+        <v>170</v>
+      </c>
+      <c r="N13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>20250313</v>
       </c>
@@ -1258,8 +1552,14 @@
         <v>0</v>
       </c>
       <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M14" t="s">
+        <v>154</v>
+      </c>
+      <c r="N14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>20250313</v>
       </c>
@@ -1290,8 +1590,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M15" t="s">
+        <v>154</v>
+      </c>
+      <c r="N15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>20250313</v>
       </c>
@@ -1322,8 +1628,14 @@
         <v>0</v>
       </c>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M16" t="s">
+        <v>182</v>
+      </c>
+      <c r="N16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>20250313</v>
       </c>
@@ -1354,8 +1666,14 @@
         <v>0</v>
       </c>
       <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M17" t="s">
+        <v>154</v>
+      </c>
+      <c r="N17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>20250320</v>
       </c>
@@ -1386,8 +1704,14 @@
         <v>0</v>
       </c>
       <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M18" t="s">
+        <v>154</v>
+      </c>
+      <c r="N18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>20250320</v>
       </c>
@@ -1420,8 +1744,17 @@
         <v>0</v>
       </c>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>20250320</v>
       </c>
@@ -1454,8 +1787,14 @@
         <v>0</v>
       </c>
       <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20250320</v>
       </c>
@@ -1488,8 +1827,17 @@
         <v>0</v>
       </c>
       <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>168</v>
+      </c>
+      <c r="N21" t="s">
+        <v>132</v>
+      </c>
+      <c r="O21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20250320</v>
       </c>
@@ -1522,8 +1870,14 @@
         <v>0</v>
       </c>
       <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M22" t="s">
+        <v>154</v>
+      </c>
+      <c r="N22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>20250320</v>
       </c>
@@ -1554,8 +1908,14 @@
         <v>0</v>
       </c>
       <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M23" t="s">
+        <v>154</v>
+      </c>
+      <c r="N23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20250320</v>
       </c>
@@ -1588,8 +1948,14 @@
         <v>0</v>
       </c>
       <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M24" t="s">
+        <v>136</v>
+      </c>
+      <c r="N24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>20250320</v>
       </c>
@@ -1622,8 +1988,17 @@
         <v>0</v>
       </c>
       <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M25" t="s">
+        <v>172</v>
+      </c>
+      <c r="N25" t="s">
+        <v>173</v>
+      </c>
+      <c r="O25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>20250320</v>
       </c>
@@ -1654,8 +2029,17 @@
         <v>0</v>
       </c>
       <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M26" t="s">
+        <v>172</v>
+      </c>
+      <c r="N26" t="s">
+        <v>173</v>
+      </c>
+      <c r="O26" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>20250320</v>
       </c>
@@ -1688,8 +2072,14 @@
         <v>0</v>
       </c>
       <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M27" t="s">
+        <v>136</v>
+      </c>
+      <c r="N27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>20250320</v>
       </c>
@@ -1722,8 +2112,17 @@
         <v>0</v>
       </c>
       <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M28" t="s">
+        <v>172</v>
+      </c>
+      <c r="N28" t="s">
+        <v>132</v>
+      </c>
+      <c r="O28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>20250320</v>
       </c>
@@ -1756,8 +2155,14 @@
         <v>0</v>
       </c>
       <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M29" t="s">
+        <v>128</v>
+      </c>
+      <c r="N29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20250320</v>
       </c>
@@ -1788,8 +2193,14 @@
         <v>0</v>
       </c>
       <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M30" t="s">
+        <v>128</v>
+      </c>
+      <c r="N30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>20250320</v>
       </c>
@@ -1820,8 +2231,17 @@
         <v>0</v>
       </c>
       <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M31" t="s">
+        <v>175</v>
+      </c>
+      <c r="N31" t="s">
+        <v>174</v>
+      </c>
+      <c r="O31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>20250320</v>
       </c>
@@ -1854,8 +2274,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M32" t="s">
+        <v>175</v>
+      </c>
+      <c r="N32" t="s">
+        <v>129</v>
+      </c>
+      <c r="O32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>20250320</v>
       </c>
@@ -1886,8 +2315,17 @@
         <v>0</v>
       </c>
       <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M33" t="s">
+        <v>175</v>
+      </c>
+      <c r="N33" t="s">
+        <v>155</v>
+      </c>
+      <c r="O33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>20250320</v>
       </c>
@@ -1918,8 +2356,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M34" t="s">
+        <v>136</v>
+      </c>
+      <c r="N34" t="s">
+        <v>131</v>
+      </c>
+      <c r="O34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>20250320</v>
       </c>
@@ -1952,8 +2399,14 @@
       <c r="L35" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M35" t="s">
+        <v>175</v>
+      </c>
+      <c r="N35" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>20250325</v>
       </c>
@@ -1986,8 +2439,11 @@
         <v>0</v>
       </c>
       <c r="L36" s="3"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M36" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>20250325</v>
       </c>
@@ -2020,8 +2476,11 @@
         <v>0</v>
       </c>
       <c r="L37" s="3"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M37" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>20250325</v>
       </c>
@@ -2054,8 +2513,11 @@
         <v>0</v>
       </c>
       <c r="L38" s="3"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>20250325</v>
       </c>
@@ -2088,8 +2550,11 @@
         <v>0</v>
       </c>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M39" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>20250325</v>
       </c>
@@ -2122,8 +2587,11 @@
         <v>0</v>
       </c>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M40" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>20250325</v>
       </c>
@@ -2158,8 +2626,11 @@
       <c r="L41" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>20250325</v>
       </c>
@@ -2192,8 +2663,11 @@
         <v>0</v>
       </c>
       <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>20250325</v>
       </c>
@@ -2226,8 +2700,11 @@
       <c r="L43" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>20250325</v>
       </c>
@@ -2260,8 +2737,11 @@
         <v>0</v>
       </c>
       <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M44" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>20250325</v>
       </c>
@@ -2294,8 +2774,11 @@
         <v>0</v>
       </c>
       <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M45" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>20250325</v>
       </c>
@@ -2328,8 +2811,11 @@
         <v>0</v>
       </c>
       <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M46" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>20250325</v>
       </c>
@@ -2362,8 +2848,11 @@
         <v>0</v>
       </c>
       <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>20250325</v>
       </c>
@@ -2396,8 +2885,11 @@
         <v>0</v>
       </c>
       <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>20250325</v>
       </c>
@@ -2430,8 +2922,11 @@
         <v>0</v>
       </c>
       <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M49" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>20250415</v>
       </c>
@@ -2464,8 +2959,14 @@
         <v>0</v>
       </c>
       <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M50" t="s">
+        <v>168</v>
+      </c>
+      <c r="N50" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>20250415</v>
       </c>
@@ -2498,8 +2999,14 @@
         <v>0</v>
       </c>
       <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M51" t="s">
+        <v>128</v>
+      </c>
+      <c r="N51" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>20250415</v>
       </c>
@@ -2532,8 +3039,14 @@
         <v>0</v>
       </c>
       <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M52" t="s">
+        <v>154</v>
+      </c>
+      <c r="N52" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>20250415</v>
       </c>
@@ -2566,8 +3079,14 @@
         <v>0</v>
       </c>
       <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M53" t="s">
+        <v>168</v>
+      </c>
+      <c r="N53" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>20250415</v>
       </c>
@@ -2600,8 +3119,14 @@
         <v>0</v>
       </c>
       <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M54" t="s">
+        <v>136</v>
+      </c>
+      <c r="N54" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>20250415</v>
       </c>
@@ -2634,8 +3159,14 @@
         <v>0</v>
       </c>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M55" t="s">
+        <v>154</v>
+      </c>
+      <c r="N55" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>20250415</v>
       </c>
@@ -2668,8 +3199,14 @@
         <v>0</v>
       </c>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M56" t="s">
+        <v>168</v>
+      </c>
+      <c r="N56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>20250415</v>
       </c>
@@ -2702,8 +3239,14 @@
         <v>0</v>
       </c>
       <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M57" t="s">
+        <v>136</v>
+      </c>
+      <c r="N57" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>20250415</v>
       </c>
@@ -2736,8 +3279,14 @@
         <v>0</v>
       </c>
       <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M58" t="s">
+        <v>168</v>
+      </c>
+      <c r="N58" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>20250415</v>
       </c>
@@ -2770,8 +3319,14 @@
         <v>0</v>
       </c>
       <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M59" t="s">
+        <v>137</v>
+      </c>
+      <c r="N59" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>20250415</v>
       </c>
@@ -2804,8 +3359,14 @@
         <v>0</v>
       </c>
       <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M60" t="s">
+        <v>168</v>
+      </c>
+      <c r="N60" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>20250415</v>
       </c>
@@ -2838,8 +3399,14 @@
         <v>0</v>
       </c>
       <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M61" t="s">
+        <v>136</v>
+      </c>
+      <c r="N61" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>20250416</v>
       </c>
@@ -2872,8 +3439,14 @@
         <v>0</v>
       </c>
       <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M62" t="s">
+        <v>154</v>
+      </c>
+      <c r="N62" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>20250416</v>
       </c>
@@ -2906,8 +3479,14 @@
         <v>0</v>
       </c>
       <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M63" t="s">
+        <v>136</v>
+      </c>
+      <c r="N63" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>20250416</v>
       </c>
@@ -2940,8 +3519,14 @@
         <v>0</v>
       </c>
       <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M64" t="s">
+        <v>190</v>
+      </c>
+      <c r="N64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>20250416</v>
       </c>
@@ -2974,8 +3559,14 @@
         <v>0</v>
       </c>
       <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M65" t="s">
+        <v>154</v>
+      </c>
+      <c r="N65" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>20250416</v>
       </c>
@@ -3008,8 +3599,14 @@
         <v>0</v>
       </c>
       <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M66" t="s">
+        <v>136</v>
+      </c>
+      <c r="N66" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>20250416</v>
       </c>
@@ -3042,8 +3639,14 @@
         <v>0</v>
       </c>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M67" t="s">
+        <v>168</v>
+      </c>
+      <c r="N67" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>20250416</v>
       </c>
@@ -3076,8 +3679,14 @@
         <v>0</v>
       </c>
       <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M68" t="s">
+        <v>168</v>
+      </c>
+      <c r="N68" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>20250416</v>
       </c>
@@ -3110,8 +3719,14 @@
         <v>0</v>
       </c>
       <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M69" t="s">
+        <v>168</v>
+      </c>
+      <c r="N69" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>20250416</v>
       </c>
@@ -3144,8 +3759,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M70" t="s">
+        <v>168</v>
+      </c>
+      <c r="N70" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>20250520</v>
       </c>
@@ -3178,8 +3799,14 @@
         <v>1</v>
       </c>
       <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M71" t="s">
+        <v>168</v>
+      </c>
+      <c r="N71" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>20250520</v>
       </c>
@@ -3212,8 +3839,14 @@
       <c r="L72" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M72" t="s">
+        <v>168</v>
+      </c>
+      <c r="N72" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>20250520</v>
       </c>
@@ -3246,8 +3879,14 @@
         <v>1</v>
       </c>
       <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M73" t="s">
+        <v>154</v>
+      </c>
+      <c r="N73" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>20250520</v>
       </c>
@@ -3278,8 +3917,14 @@
         <v>1</v>
       </c>
       <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M74" t="s">
+        <v>133</v>
+      </c>
+      <c r="N74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>20250520</v>
       </c>
@@ -3312,8 +3957,14 @@
         <v>1</v>
       </c>
       <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M75" t="s">
+        <v>133</v>
+      </c>
+      <c r="N75" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>20250520</v>
       </c>
@@ -3346,8 +3997,14 @@
         <v>1</v>
       </c>
       <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M76" t="s">
+        <v>168</v>
+      </c>
+      <c r="N76" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>20250520</v>
       </c>
@@ -3378,8 +4035,14 @@
         <v>1</v>
       </c>
       <c r="L77" s="3"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M77" t="s">
+        <v>154</v>
+      </c>
+      <c r="N77" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>20250520</v>
       </c>
@@ -3412,8 +4075,14 @@
       <c r="L78" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M78" t="s">
+        <v>154</v>
+      </c>
+      <c r="N78" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>20250520</v>
       </c>
@@ -3444,8 +4113,14 @@
         <v>1</v>
       </c>
       <c r="L79" s="3"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M79" t="s">
+        <v>133</v>
+      </c>
+      <c r="N79" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>20250520</v>
       </c>
@@ -3478,8 +4153,14 @@
       <c r="L80" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M80" t="s">
+        <v>136</v>
+      </c>
+      <c r="N80" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>20250520</v>
       </c>
@@ -3512,8 +4193,14 @@
         <v>1</v>
       </c>
       <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M81" t="s">
+        <v>127</v>
+      </c>
+      <c r="N81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>20250520</v>
       </c>
@@ -3544,8 +4231,14 @@
         <v>1</v>
       </c>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M82" t="s">
+        <v>133</v>
+      </c>
+      <c r="N82" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>20250520</v>
       </c>
@@ -3578,8 +4271,14 @@
         <v>1</v>
       </c>
       <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M83" t="s">
+        <v>133</v>
+      </c>
+      <c r="N83" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>20250520</v>
       </c>
@@ -3612,8 +4311,14 @@
         <v>1</v>
       </c>
       <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M84" t="s">
+        <v>154</v>
+      </c>
+      <c r="N84" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>20250520</v>
       </c>
@@ -3646,8 +4351,14 @@
         <v>1</v>
       </c>
       <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M85" t="s">
+        <v>191</v>
+      </c>
+      <c r="N85" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>20250523</v>
       </c>
@@ -3678,8 +4389,14 @@
         <v>1</v>
       </c>
       <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M86" t="s">
+        <v>157</v>
+      </c>
+      <c r="N86" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>20250523</v>
       </c>
@@ -3712,8 +4429,14 @@
       <c r="L87" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M87" t="s">
+        <v>157</v>
+      </c>
+      <c r="N87" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>20250523</v>
       </c>
@@ -3744,8 +4467,14 @@
         <v>1</v>
       </c>
       <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M88" t="s">
+        <v>157</v>
+      </c>
+      <c r="N88" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>20250523</v>
       </c>
@@ -3778,8 +4507,14 @@
       <c r="L89" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M89" t="s">
+        <v>157</v>
+      </c>
+      <c r="N89" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>20250523</v>
       </c>
@@ -3810,8 +4545,14 @@
         <v>1</v>
       </c>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M90" t="s">
+        <v>157</v>
+      </c>
+      <c r="N90" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>20250523</v>
       </c>
@@ -3844,8 +4585,14 @@
       <c r="L91" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M91" t="s">
+        <v>157</v>
+      </c>
+      <c r="N91" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>20250523</v>
       </c>
@@ -3876,8 +4623,14 @@
         <v>1</v>
       </c>
       <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M92" t="s">
+        <v>157</v>
+      </c>
+      <c r="N92" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>20250523</v>
       </c>
@@ -3910,8 +4663,14 @@
         <v>1</v>
       </c>
       <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M93" t="s">
+        <v>157</v>
+      </c>
+      <c r="N93" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>20250523</v>
       </c>
@@ -3946,8 +4705,14 @@
         <v>1</v>
       </c>
       <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M94" t="s">
+        <v>157</v>
+      </c>
+      <c r="N94" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>20250523</v>
       </c>
@@ -3980,8 +4745,14 @@
         <v>1</v>
       </c>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M95" t="s">
+        <v>157</v>
+      </c>
+      <c r="N95" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>20250523</v>
       </c>
@@ -4014,8 +4785,14 @@
         <v>1</v>
       </c>
       <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M96" t="s">
+        <v>157</v>
+      </c>
+      <c r="N96" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>20250523</v>
       </c>
@@ -4048,8 +4825,14 @@
         <v>1</v>
       </c>
       <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M97" t="s">
+        <v>157</v>
+      </c>
+      <c r="N97" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>20250523</v>
       </c>
@@ -4080,8 +4863,14 @@
         <v>1</v>
       </c>
       <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M98" t="s">
+        <v>157</v>
+      </c>
+      <c r="N98" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>20250523</v>
       </c>
@@ -4114,8 +4903,14 @@
         <v>1</v>
       </c>
       <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M99" t="s">
+        <v>157</v>
+      </c>
+      <c r="N99" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>20250523</v>
       </c>
@@ -4148,8 +4943,14 @@
         <v>1</v>
       </c>
       <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M100" t="s">
+        <v>157</v>
+      </c>
+      <c r="N100" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>20250602</v>
       </c>
@@ -4181,7 +4982,7 @@
       </c>
       <c r="L101" s="3"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>20250602</v>
       </c>
@@ -4215,7 +5016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>20250602</v>
       </c>
@@ -4247,7 +5048,7 @@
       </c>
       <c r="L103" s="3"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>20250602</v>
       </c>
@@ -4265,7 +5066,7 @@
       <c r="K104" s="1"/>
       <c r="L104" s="3"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>20250602</v>
       </c>
@@ -4283,7 +5084,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="3"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>20250602</v>
       </c>
@@ -4319,7 +5120,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>20250602</v>
       </c>
@@ -4337,7 +5138,7 @@
       <c r="K107" s="1"/>
       <c r="L107" s="3"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>20250602</v>
       </c>
@@ -4367,7 +5168,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="3"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>20250602</v>
       </c>
@@ -4389,7 +5190,7 @@
       </c>
       <c r="L109" s="3"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>20250602</v>
       </c>
@@ -4423,7 +5224,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>20250602</v>
       </c>
@@ -4441,7 +5242,7 @@
       <c r="K111" s="1"/>
       <c r="L111" s="3"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>20250602</v>
       </c>
@@ -4473,7 +5274,7 @@
       </c>
       <c r="L112" s="3"/>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>20250602</v>
       </c>
@@ -4507,7 +5308,7 @@
       </c>
       <c r="L113" s="3"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>20250604</v>
       </c>
@@ -4525,7 +5326,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="3"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>20250604</v>
       </c>
@@ -4561,7 +5362,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>20250604</v>
       </c>
@@ -4579,7 +5380,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="3"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>20250604</v>
       </c>
@@ -4613,7 +5414,7 @@
       </c>
       <c r="L117" s="3"/>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>20250604</v>
       </c>
@@ -4631,7 +5432,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="3"/>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>20250604</v>
       </c>
@@ -4667,7 +5468,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>20250604</v>
       </c>
@@ -4685,7 +5486,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="3"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>20250604</v>
       </c>
@@ -4703,7 +5504,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="3"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>20250604</v>
       </c>
@@ -4721,7 +5522,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="3"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>20250604</v>
       </c>
@@ -4753,7 +5554,7 @@
       </c>
       <c r="L123" s="3"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>20250604</v>
       </c>
@@ -4787,7 +5588,7 @@
       </c>
       <c r="L124" s="3"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>20250604</v>
       </c>
@@ -4805,7 +5606,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="3"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>20250604</v>
       </c>
@@ -4841,7 +5642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>20250604</v>
       </c>
@@ -4859,7 +5660,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="3"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>20250604</v>
       </c>
@@ -4877,7 +5678,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="3"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>20250604</v>
       </c>
@@ -4911,7 +5712,7 @@
       </c>
       <c r="L129" s="3"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>20250604</v>
       </c>
@@ -4945,7 +5746,7 @@
       </c>
       <c r="L130" s="3"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>20250605</v>
       </c>
@@ -4963,7 +5764,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="3"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>20250605</v>
       </c>
@@ -4997,7 +5798,7 @@
       </c>
       <c r="L132" s="3"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>20250605</v>
       </c>
@@ -5031,7 +5832,7 @@
       </c>
       <c r="L133" s="3"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>20250605</v>
       </c>
@@ -5063,7 +5864,7 @@
       </c>
       <c r="L134" s="3"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>20250605</v>
       </c>
@@ -5099,7 +5900,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>20250605</v>
       </c>
@@ -5133,7 +5934,7 @@
       </c>
       <c r="L136" s="3"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>20250609</v>
       </c>
@@ -5150,8 +5951,11 @@
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
       <c r="L137" s="3"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M137" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>20250609</v>
       </c>
@@ -5169,7 +5973,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="3"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>20250609</v>
       </c>
@@ -5187,7 +5991,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="3"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>20250609</v>
       </c>
@@ -5205,7 +6009,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="3"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>20250609</v>
       </c>
@@ -5223,7 +6027,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="3"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>20250609</v>
       </c>
@@ -5241,7 +6045,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="3"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>20250609</v>
       </c>
@@ -5259,7 +6063,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="3"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>20250609</v>
       </c>
@@ -5277,7 +6081,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="3"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>20250609</v>
       </c>
@@ -5313,7 +6117,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>20250609</v>
       </c>
@@ -5347,7 +6151,7 @@
       </c>
       <c r="L146" s="3"/>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>20250609</v>
       </c>
@@ -5383,7 +6187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>20250610</v>
       </c>
@@ -5400,8 +6204,14 @@
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
       <c r="L148" s="3"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M148" t="s">
+        <v>136</v>
+      </c>
+      <c r="N148" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>20250610</v>
       </c>
@@ -5418,8 +6228,14 @@
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
       <c r="L149" s="3"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M149" t="s">
+        <v>154</v>
+      </c>
+      <c r="N149" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>20250610</v>
       </c>
@@ -5436,8 +6252,14 @@
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
       <c r="L150" s="3"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M150" t="s">
+        <v>154</v>
+      </c>
+      <c r="N150" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>20250610</v>
       </c>
@@ -5454,8 +6276,14 @@
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
       <c r="L151" s="3"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M151" t="s">
+        <v>154</v>
+      </c>
+      <c r="N151" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>20250610</v>
       </c>
@@ -5472,8 +6300,14 @@
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
       <c r="L152" s="3"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M152" t="s">
+        <v>154</v>
+      </c>
+      <c r="N152" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>20250610</v>
       </c>
@@ -5502,8 +6336,14 @@
       <c r="L153" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M153" t="s">
+        <v>154</v>
+      </c>
+      <c r="N153" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>20250611</v>
       </c>
@@ -5520,8 +6360,11 @@
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
       <c r="L154" s="3"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M154" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>20250611</v>
       </c>
@@ -5538,8 +6381,11 @@
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
       <c r="L155" s="3"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M155" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>20250611</v>
       </c>
@@ -5556,8 +6402,11 @@
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
       <c r="L156" s="3"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M156" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>20250611</v>
       </c>
@@ -5590,8 +6439,11 @@
       <c r="L157" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M157" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>20250611</v>
       </c>
@@ -5624,8 +6476,11 @@
       <c r="L158" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>20250611</v>
       </c>
@@ -5642,8 +6497,11 @@
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
       <c r="L159" s="3"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M159" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>20250611</v>
       </c>
@@ -5676,8 +6534,11 @@
       <c r="L160" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M160" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>20250611</v>
       </c>
@@ -5694,8 +6555,11 @@
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
       <c r="L161" s="3"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M161" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>20250611</v>
       </c>
@@ -5712,8 +6576,11 @@
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
       <c r="L162" s="3"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M162" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>20250613</v>
       </c>
@@ -5748,8 +6615,11 @@
       <c r="L163" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M163" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>20250613</v>
       </c>
@@ -5766,8 +6636,11 @@
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
       <c r="L164" s="3"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M164" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>20250613</v>
       </c>
@@ -5784,8 +6657,11 @@
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
       <c r="L165" s="3"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M165" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>20250613</v>
       </c>
@@ -5802,8 +6678,11 @@
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
       <c r="L166" s="3"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M166" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>20250613</v>
       </c>
@@ -5820,8 +6699,11 @@
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
       <c r="L167" s="3"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M167" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>20250613</v>
       </c>
@@ -5838,8 +6720,11 @@
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
       <c r="L168" s="3"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M168" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>20250613</v>
       </c>
@@ -5856,8 +6741,11 @@
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
       <c r="L169" s="3"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M169" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>20250613</v>
       </c>
@@ -5874,8 +6762,11 @@
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
       <c r="L170" s="3"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M170" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>20250613</v>
       </c>
@@ -5910,8 +6801,11 @@
       <c r="L171" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M171" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>20250613</v>
       </c>
@@ -5944,8 +6838,11 @@
         <v>1</v>
       </c>
       <c r="L172" s="3"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M172" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>20250613</v>
       </c>
@@ -5962,8 +6859,11 @@
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
       <c r="L173" s="3"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M173" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>20250613</v>
       </c>
@@ -5980,8 +6880,11 @@
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
       <c r="L174" s="3"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M174" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>20250613</v>
       </c>
@@ -5998,8 +6901,11 @@
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
       <c r="L175" s="3"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M175" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>20250615</v>
       </c>
@@ -6016,8 +6922,11 @@
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
       <c r="L176" s="3"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M176" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>20250615</v>
       </c>
@@ -6052,8 +6961,11 @@
       <c r="L177" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M177" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>20250615</v>
       </c>
@@ -6086,8 +6998,11 @@
         <v>1</v>
       </c>
       <c r="L178" s="3"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M178" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>20250615</v>
       </c>
@@ -6120,8 +7035,11 @@
         <v>1</v>
       </c>
       <c r="L179" s="3"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M179" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>20250615</v>
       </c>
@@ -6154,8 +7072,11 @@
         <v>1</v>
       </c>
       <c r="L180" s="3"/>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M180" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>20250615</v>
       </c>
@@ -6188,8 +7109,11 @@
         <v>1</v>
       </c>
       <c r="L181" s="3"/>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M181" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>20250615</v>
       </c>
@@ -6222,8 +7146,11 @@
         <v>1</v>
       </c>
       <c r="L182" s="3"/>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M182" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>20250615</v>
       </c>
@@ -6258,8 +7185,11 @@
       <c r="L183" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M183" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>20250615</v>
       </c>
@@ -6294,8 +7224,11 @@
       <c r="L184" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M184" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>20250615</v>
       </c>
@@ -6330,8 +7263,11 @@
         <v>1</v>
       </c>
       <c r="L185" s="3"/>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M185" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>20250615</v>
       </c>
@@ -6364,8 +7300,11 @@
         <v>1</v>
       </c>
       <c r="L186" s="3"/>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M186" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>20250615</v>
       </c>
@@ -6400,8 +7339,11 @@
       <c r="L187" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M187" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>20250615</v>
       </c>
@@ -6436,8 +7378,11 @@
       <c r="L188" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M188" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>20250615</v>
       </c>
@@ -6470,8 +7415,11 @@
         <v>1</v>
       </c>
       <c r="L189" s="3"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M189" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>20250615</v>
       </c>
@@ -6504,8 +7452,11 @@
         <v>1</v>
       </c>
       <c r="L190" s="3"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M190" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>20250615</v>
       </c>
@@ -6536,8 +7487,11 @@
         <v>1</v>
       </c>
       <c r="L191" s="3"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M191" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>20250615</v>
       </c>
@@ -6572,6 +7526,9 @@
         <v>1</v>
       </c>
       <c r="L192" s="3"/>
+      <c r="M192" t="s">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
